--- a/Result/checksun_type/機電工程.xlsx
+++ b/Result/checksun_type/機電工程.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>29.72</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>127333994.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>136119460.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>136119460.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>180700080.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>145391726.86</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>145391726.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-613552.485242337</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>127333994</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>127333994.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>29.47</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>29.81</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>96388822.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>138332873.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>138332873.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>180043930.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>147065410.9</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>147065410.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>2060029.688120633</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>96388822</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>96388822.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>29.33</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>29.87</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>230366989.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>203567123.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>203567123.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>176748876.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>147814262.16</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>147814262.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>9121414.446920574</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>230366989</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>230366989.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>29.88</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>115162110.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>195906349.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>195906349.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>159890084.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>146325446.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>146325446.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>4528538.550673336</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>115162110</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>115162110.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>29.48</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>29.93</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>29.91</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29.91</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>111345387.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>224691822.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>224691822.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>155503621.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>147839532.26</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>147839532.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>10148933.64351037</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>111345387</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>111345387.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>29.69</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>29.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>138401058.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>225280701.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>225280701.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>153817007.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>152621564.4</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>152621564.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>18224542.18172359</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>138401058</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>138401058.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>30.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>422560072.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>221754987.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>221754987.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>148259755.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>165846039.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>165846039.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>26211427.40839526</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>422560072</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>422560072.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30.03</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>192063122.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>149930629.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>149930629.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>120348042.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>159096343.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>159096343.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>6239532.396197796</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>192063122</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>192063122.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>30.11</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>259089472.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>123873819.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>123873819</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>112679035.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>157358151.42</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>157358151.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2181515.150337219</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>259089472</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>259089472.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>29.97</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>114289782.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>86315421.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>86315421.59999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>100819006.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>155312221.68</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>155312221.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-10874958.24197567</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>114289782</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>114289782.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>29.93</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>30.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>120772490.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>82353314.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>82353314.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>100638773.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>158831737.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>158831737.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13624419.22235207</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>120772490</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>120772490.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>39.62</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>40.71</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40.71</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>54337.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16739.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16739.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>13814.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>12554.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>12554.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>2974.684800845385</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>54337</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>54337.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>39.34</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>10062.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>8003.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>8003</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>9548.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>12075.34</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>12075.34</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-487.1305148239862</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10062</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10062.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>38.76000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>39.35</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>40.83</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40.83</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4288.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>9006.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>9006</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>9246.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>12404.82</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>12404.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-671.433447393656</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4288</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4288.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>38.72</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>8716.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>11437.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>11437.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>9715.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>12725.54</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>12725.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-292.1007279434089</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>8716</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>8716.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>38.88</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>6295.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>11082.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>11082.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>9627.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>12959.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>12959.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-214.193245587936</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>6295</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>6295.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>39.07000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.13</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.13</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>10654.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>10888.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>10888.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>9749.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13307.86</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13307.86</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>164.1457736908815</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>10654</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>10654.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>39.33</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>39.77</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.25</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.25</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>15077.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>11093.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>11093</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>10023.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>14444.66</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>14444.66</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>231.7320236002288</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>15077</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>15077.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>39.48</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>39.89</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>16444.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>9487.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>9487.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>10087.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>15169.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>15169.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-153.8851916578515</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>16444</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>16444.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>39.54</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.45</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>6941.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>7994.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>7994.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>9181.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>15189.72</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>15189.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-845.7353137530426</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>6941</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>6941.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>39.45</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>40.05</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.52</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.52</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5326.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8172.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>8172</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9082.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>15581.78</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>15581.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-785.7092269692785</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5326</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5326.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>39.32000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>11677.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>8610.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>8610.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10561.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>16312.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>16312.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-498.8609163149977</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>11677</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>11677.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>25.34</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.51</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.51</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2135.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>800.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-19.60460430157423</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2135</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2135.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>25.99</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28.63</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>28.63</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1285.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>467.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>467.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>632.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-139.9302155402339</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1285</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1285.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>26.5</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>28.34</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28.74</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>160.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>392.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>392.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>584.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-215.7550096118822</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>160</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.86</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>28.84</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>28.84</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>406.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>427.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>427.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>762.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-195.8348936566698</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>406</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>406.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>216.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>663.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>663.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>970.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-186.7406246614853</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>216</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>29.02</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>270.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>759.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>759.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1025.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-146.7223609304546</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>270</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>27.59</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29.05</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>909.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>798.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>798.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1511.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-90.09904271003711</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>909</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>909.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.68</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.09</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>335.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>777.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>777</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1962.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-74.45505086979642</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>335</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>335.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>27.97</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.12</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1588.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1097.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1097.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2273.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>12.05261786161145</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1588</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1588.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.21</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.21</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>697.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1277.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1277.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2136.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>0.9545511257081216</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>697</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>697.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>29.65</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>463.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1290.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1290.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2149.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>80.53036467707079</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>463</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>463.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>44.35</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>45.01</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>46.49</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>46.49</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4028.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>4253.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>4253.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>6048.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>12417.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>12417.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1375.557454305219</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4028</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4028.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>43.81</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>45.04</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>46.53</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2365.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>3950.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>3950</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>6189.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>12708.58</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>12708.58</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1411.912934877047</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2365</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2365.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>43.43</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>45.07</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>46.58</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>46.58</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>3632.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5146.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5146</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6778.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>12819.56</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>12819.56</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1235.245302305477</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>3632</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>3632.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>43.3</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>46.64</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>6020.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>6904.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>6904.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>9089.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>12882.3</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>12882.3</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1074.497066406609</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>6020</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>6020.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>43.54000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>45.27</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>45.27</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>46.72</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>5224.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>6894.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>6894</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>9115.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>12961.68</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>12961.68</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1062.338977036562</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>5224</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>5224.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>43.82000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>46.77</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>46.77</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2509.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>7842.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>7842.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>9282.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>12964.82</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>12964.82</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-921.7438858994756</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2509</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2509.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>44.33</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>45.53</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>46.86</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>46.86</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>8345.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>8428.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>8428.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>10424.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>13047.02</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>13047.02</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-397.0814740643691</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>8345</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>8345.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>44.67</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>45.68</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>46.93</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>12425.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>8410.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>8410.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>12897.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>12949.98</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>12949.98</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-258.6679759404906</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>12425</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>12425.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>44.83</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>46.98</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>46.98</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>5967.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>11274.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>11274.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>13300.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>12830.78</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>12830.78</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-488.8391223370745</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>5967</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>5967.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>45.22</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>45.82</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>47.01</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>9966.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>11336.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>11336.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>13391.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>12963.58</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>12963.58</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-108.2679342487281</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>9966</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>9966.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>45.61</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>47.04</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>47.04</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>5440.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>10723.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>10723.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>12872.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>12982.24</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>12982.24</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>10.80761781493493</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>5440</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>5440.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>661.0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>693.85</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>757.74</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>693.85</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>757.74</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>712958.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>792037.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>792037</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1109041.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1587746.18</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1587746.18</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-180463.9620508341</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>712958</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>712958.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>661.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>698.65</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>763.12</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>698.65</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>763.12</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>625808.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1047539.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1047539.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1197029.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1609718.98</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1609718.98</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-173323.4371483272</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>625808</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>625808.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>654.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>701.8</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>768.9</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>701.8</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>768.9</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>643959.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1163874.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1163874.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1469582.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1641057.24</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1641057.24</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-147595.0645323058</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>643959</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>643959.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>657.6</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>705.65</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>775.68</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>775.6799999999999</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>706601.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1264658.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1264658.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1638238.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1667740.04</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1667740.04</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-107513.7442046928</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>706601</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>706601.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>709.9</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>781.92</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>781.92</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1270859.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1337944.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1337944.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1646579.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1693766.7</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1693766.7</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-53126.58144364925</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1270859</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1270859.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>659.8</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>713.75</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>787.68</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>713.75</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>787.6799999999999</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1990469.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1426046.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1426046</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1661220.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1766700.72</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1766700.72</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-33989.47101917118</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1990469</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1990469.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>653.2</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>720.2</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>792.16</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>720.2</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>792.16</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1207486.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1346519.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1346519.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1548234.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1812003.46</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1812003.46</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-82537.90359066054</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1207486</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1207486.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>655.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>728.45</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>796.64</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>796.64</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1147878.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1775289.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1775289.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1535904.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1855325.14</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1855325.14</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-65053.98927883594</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1147878</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1147878.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>659.0</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>736.75</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>802.06</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>736.75</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>802.0599999999999</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1073032.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>2011819.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>2011819.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1515893.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1946359.3</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1946359.3</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-31367.04064484267</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1073032</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1073032.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>679.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>747.95</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>808.66</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>747.95</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>808.66</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1711365.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1955214.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1955214.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1550532.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2038998.2</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2038998.2</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>25896.6374267491</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1711365</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1711365.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>694.0</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>757.8</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>812.84</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>757.8</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>812.84</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1592835.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1896394.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1896394.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1630314.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2070739.62</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2070739.62</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>38384.19047806808</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1592835</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1592835.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>11.91</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>12.26</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>13.12</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>300765.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>243544.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>243544.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>262013.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>397813.1</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>397813.1</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-46609.19585511688</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>300765</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>300765.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>11.92</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>69834.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>231465.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>231465.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>359852.1</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>394035.44</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>394035.44</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-55324.48139847646</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>69834</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>69834.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>11.96</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>13.22</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>357229.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>281513.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>281513.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>389907.1</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>400047.44</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>400047.44</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-41056.40783904452</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>357229</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>357229.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>12.03</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>13.26</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>204139.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>234416.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>234416</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>361873.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>403142.8</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>403142.8</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-49999.4667598902</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>204139</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>204139.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>12.09</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>12.47</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>285754.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>236856.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>236856.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>351502.0</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>407570.42</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>407570.42</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-44587.06997681648</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>285754</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>285754.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>12.14</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>12.54</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>13.35</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>240371.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>280483.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>280483.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>359858.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>411381.72</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>411381.72</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-44007.14350182493</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>240371</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>240371.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>12.61</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>13.4</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>320074.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>488238.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>488238.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>351314.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>411196.04</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>411196.04</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-36744.52912677184</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>320074</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>320074.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>12.21</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>13.44</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>121742.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>498300.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>498300.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>443770.8</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>418441.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>418441.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-33596.66826502554</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>121742</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>121742.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>12.27</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>13.49</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>13.49</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>216343.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>489330.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>489330.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>566870.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>417275.34</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>417275.34</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-6649.986024494283</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>216343</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>216343.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>12.33</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>13.54</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>13.54</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>503887.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>466147.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>466147.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>592315.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>416633.44</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>416633.44</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>21946.95239142526</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>503887</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>503887.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>12.38</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>13.59</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>13.59</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1279148.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>439233.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>439233.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>562979.8</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>408016.16</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>408016.16</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>31207.61611447355</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1279148</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1279148.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>165.6</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>163.02</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>160.83</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>160.83</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>74566654.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>58486136.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>58486136.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>58606873.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>70642832.02</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>70642832.02</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1307560.096186429</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>74566654</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>74566654.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>163.7</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>160.46</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>160.46</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>42057189.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>51280880.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>51280880.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>57575110.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>70368392.78</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>70368392.78</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-2977612.849109128</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>42057189</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>42057189.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>163.1</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>160.23</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>160.23</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>86690785.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>57113679.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>57113679.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>64547068.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>70595791.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>70595791.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-1773902.21581623</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>86690785</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>86690785.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>161.6</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>163.32</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>160.05</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>160.05</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>60623888.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>52450873.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>52450873.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>60032236.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>69475167.82</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>69475167.81999999</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-4773132.94626151</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>60623888</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>60623888.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>160.4</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>163.85</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>159.88</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>163.85</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>159.88</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>28492168.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>47694181.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>47694181</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>56493562.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>68696315.04</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>68696315.04000001</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-6094397.420245431</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>28492168</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>28492168.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>159.4</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>164.42</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>159.69</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>159.69</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>38540371.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>58727610.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>58727610.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>57494793.8</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>69451049.8</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>69451049.8</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-4321576.760927983</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>38540371</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>38540371.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>164.95</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>159.6</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>159.6</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>71221184.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>63869339.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>63869339.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>58008720.2</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>70188106.76</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>70188106.76000001</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-2711226.970441341</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>71221184</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>71221184.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>158.9</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>165.38</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>159.41</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>165.38</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>159.41</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>63376756.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>71980458.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>71980458.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>59415753.1</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>69152957.06</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>69152957.06</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-3815413.413658947</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>63376756</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>63376756.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>159.3</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>165.7</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>159.21</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>159.21</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>36840426.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>67613598.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>67613598.59999999</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>63171366.2</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>68561486.4</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>68561486.40000001</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-4416083.42491056</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>36840426</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>36840426.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>160.8</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>166.2</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>159.08</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>159.08</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>83659315.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>65292944.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>65292944.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>63664049.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>69466030.4</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>69466030.40000001</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-2273287.961523205</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>83659315</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>83659315.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>166.95</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>158.97</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>166.95</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>158.97</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>64249018.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>56261977.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>56261977.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>58685909.5</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>68228488.76</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>68228488.76000001</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-4147272.265201129</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>64249018</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>64249018.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>403535423</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>363440217</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>451484020</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>569640781</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1056628890</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>436450840</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>365688993</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>676579414</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>622810797</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>566992376</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>832928036</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>10702402903</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>9579043601</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>16911194399</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>15812987742</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>15882778006</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>10973548400</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>12353712685</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>10709769939</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>18182742782</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>10733728288</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>13958553198</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>2683545818</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>4682266073</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>11515775721</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3032171594</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>3089667541</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>2778009293</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>3068959808</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>3989400881</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>7366534520</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>5064644998</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>1385646995</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>176.35</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>178.66</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>178.66</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>237989780.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>367839281.4</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>367839281.4</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>390785616.2</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>619088599.9</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>619088599.9</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-136007795.8903053</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>237989780</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>237989780.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>163.3</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>176.75</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>179.19</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>179.19</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>159879057.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>390309422.8</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>390309422.8</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>388711962.0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>624204896.68</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>624204896.6799999</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-136759988.5246557</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>159879057</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>159879057.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>163.2</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>177.4</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>179.87</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>179.87</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>281592910.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>454120103.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>454120103</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>408623891.0</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>634139495.34</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>634139495.34</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-124581258.0907041</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>281592910</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>281592910.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>178.15</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>180.47</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>180.47</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>661439743.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>465917519.0</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>465917519</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>425236210.1</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>640116204.56</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>640116204.5599999</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-115774511.0746768</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>661439743</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>661439743.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>165.8</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>178.8</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>181.02</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>181.02</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>498294917.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>454526412.0</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>454526412</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>417725808.9</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>631196639.66</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>631196639.66</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-139756514.9062564</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>498294917</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>498294917.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>167.8</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>179.3</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>181.48</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>181.48</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>350340487.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>413731951.0</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>413731951</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>411216325.6</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>634370543.96</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>634370543.96</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-151545413.4904325</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>350340487</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>350340487.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>170.7</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>179.98</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>182.09</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>182.09</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>478932458.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>387114501.2</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>387114501.2</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>473719052.0</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>647350541.68</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>647350541.6799999</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-147122100.6288829</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>478932458</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>478932458.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>173.6</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>180.65</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>182.55</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>182.55</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>340579990.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>363127679.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>363127679</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>670451790.8</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>644918717.5</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>644918717.5</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-149326432.6970662</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>340579990</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>340579990.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>181.12</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>182.92</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>181.12</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>182.92</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>604484208.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>384554901.2</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>384554901.2</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>1377596235.0</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>654170853.0</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>654170853</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-132318912.9124327</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>604484208</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>604484208.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>177.8</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>181.55</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>183.34</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>183.34</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>294322612.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>380925205.8</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>380925205.8</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>1777576263.3</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>698405618.96</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>698405618.96</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-131572232.5446552</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>294322612</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>294322612.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>181.42</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>183.81</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>183.81</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>217253238.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>408700700.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>408700700.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>1872522206.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>746966653.34</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>746966653.34</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-92574938.4283781</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>217253238</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>217253238.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>91.22</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>91.09</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>90.58</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>90.58</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>5426473.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>2041452.4</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>2041452.4</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>2053581.0</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>3244658.6</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>3244658.6</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>31497.49104282586</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>5426473</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>5426473.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>91.32000000000001</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>91.06</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>90.58</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>90.58</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>278471.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>1177595.6</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>1177595.6</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>1873628.9</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>3198333.56</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>3198333.56</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-293096.237280078</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>278471</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>278471.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>91.28</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>91.04</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>90.58</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>90.58</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>3295836.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>1831654.2</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>1831654.2</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>2018901.4</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>3247624.7</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>3247624.7</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-194762.197838509</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>3295836</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>3295836.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>91.18</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>91.04</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>90.57</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>90.56999999999999</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>649041.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>1281910.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>1281910.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>1734397.8</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>3244898.94</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>3244898.94</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-370618.312999178</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>649041</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>649041.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>91.35999999999999</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>91.07</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>90.59</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>91.06999999999999</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>90.59</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>557441.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>1988106.2</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>1988106.2</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>1804943.7</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>3250755.4</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>3250755.4</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-325019.7877644489</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>557441</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>557441.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>91.3</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>91.06</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>90.59</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>90.59</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>1107189.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>2065709.6</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>2065709.6</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>1839797.5</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>3268900.24</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>3268900.24</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-238456.9021518198</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>1107189</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>1107189.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>91.44</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>90.96</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>90.58</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>90.58</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>3548764.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>2569662.2</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>2569662.2</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>1858502.9</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>3250417.4</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>3250417.4</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-165180.8904854991</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>3548764</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>3548764.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>91.46000000000001</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>90.92</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>90.59</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>90.59</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>547119.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>2206148.6</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>2206148.6</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>1596022.6</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>3210808.9</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>3210808.9</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-316198.8777305593</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>547119</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>547119.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>91.32</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>90.9</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>90.57</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>90.56999999999999</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>4180018.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>2186884.8</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>2186884.8</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>1679254.8</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>3251977.76</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>3251977.76</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-199041.2210188392</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>4180018</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>4180018.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>91.12</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>90.82</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>90.54</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>90.54000000000001</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>945458.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>1621781.2</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>1621781.2</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>2263570.5</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>3202848.92</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>3202848.92</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-413803.7035371375</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>945458</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>945458.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>91.0</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>90.76</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>3626952.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>1613885.4</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>1613885.4</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>2508333.9</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>3369940.14</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>3369940.14</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-359268.5462940945</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>3626952</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>3626952.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
